--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,17 +854,17 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="14">
         <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="14">
-        <v>2</v>
       </c>
       <c r="H14" s="15">
         <v>-100</v>
@@ -923,7 +923,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="N15" s="15">
         <v>0</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
+        <v>10</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-30</v>
+      </c>
+      <c r="I16" s="14">
         <v>9</v>
       </c>
-      <c r="H16" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I16" s="14">
-        <v>6</v>
-      </c>
       <c r="J16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-64.705882352941</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.181818181818</v>
+        <v>-90.816326530612</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
         <v>1</v>
       </c>
-      <c r="D17" s="14">
-        <v>4</v>
-      </c>
       <c r="E17" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I17" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J17" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="15">
-        <v>11.764705882352</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>-26.923076923076</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M17" s="15">
-        <v>72.727272727272</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>72.727272727272</v>
+        <v>46.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>16.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>180</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N18" s="15">
-        <v>-66.666666666666</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,48 +1057,48 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="K19" s="15">
-        <v>22.727272727272</v>
+        <v>16</v>
       </c>
       <c r="L19" s="15">
-        <v>45.945945945945</v>
+        <v>38.095238095238</v>
       </c>
       <c r="M19" s="15">
-        <v>157.142857142857</v>
+        <v>132</v>
       </c>
       <c r="N19" s="15">
-        <v>63.636363636363</v>
+        <v>31.818181818181</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-85.714285714285</v>
+        <v>-87.5</v>
       </c>
       <c r="M20" s="15">
         <v>-85.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.619047619047</v>
+        <v>-98</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.555555555555</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="F21" s="17">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.594202898550</v>
+        <v>-13.432835820895</v>
       </c>
       <c r="I21" s="17">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="J21" s="17">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="K21" s="18">
-        <v>7.954545454545</v>
+        <v>5.940594059405</v>
       </c>
       <c r="L21" s="18">
-        <v>0</v>
+        <v>-1.834862385321</v>
       </c>
       <c r="M21" s="18">
-        <v>53.225806451612</v>
+        <v>57.352941176470</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.62100456621</v>
+        <v>-57.874015748031</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>5</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K23" s="15">
-        <v>31.25</v>
+        <v>52.941176470588</v>
       </c>
       <c r="L23" s="15">
-        <v>31.25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M23" s="15">
-        <v>40</v>
+        <v>73.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>60</v>
+        <v>-15</v>
       </c>
       <c r="F24" s="14">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>22.784810126582</v>
+        <v>5.747126436781</v>
       </c>
       <c r="I24" s="14">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="J24" s="14">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="K24" s="15">
-        <v>23.300970873786</v>
+        <v>17.886178861788</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.78125</v>
+        <v>5.839416058394</v>
       </c>
       <c r="M24" s="15">
-        <v>86.764705882352</v>
+        <v>79.012345679012</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>85.714285714285</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="H25" s="15">
-        <v>13.953488372093</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="I25" s="14">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J25" s="14">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K25" s="15">
-        <v>25</v>
+        <v>12.121212121212</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.529411764705</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-69.230769230769</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H26" s="15">
-        <v>-51.162790697674</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I26" s="14">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K26" s="15">
-        <v>-27.659574468085</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="L26" s="15">
-        <v>-29.166666666666</v>
+        <v>-20</v>
       </c>
       <c r="M26" s="15">
-        <v>9.677419354838</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>20</v>
+        <v>50</v>
+      </c>
+      <c r="I28" s="14">
+        <v>3</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>-100</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>-50</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
+        <v>9</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="I16" s="14">
         <v>10</v>
       </c>
-      <c r="H16" s="15">
-        <v>-30</v>
-      </c>
-      <c r="I16" s="14">
-        <v>9</v>
-      </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L16" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.058823529411</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="N16" s="15">
-        <v>-90.816326530612</v>
+        <v>-91.452991452991</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.384615384615</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I17" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J17" s="14">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>22.222222222222</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="L17" s="15">
-        <v>-29.032258064516</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>78.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>46.666666666666</v>
+        <v>31.578947368421</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.111111111111</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="L18" s="15">
-        <v>6.666666666666</v>
+        <v>31.25</v>
       </c>
       <c r="M18" s="15">
-        <v>166.666666666667</v>
+        <v>200</v>
       </c>
       <c r="N18" s="15">
-        <v>-63.636363636363</v>
+        <v>-57.142857142857</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.666666666666</v>
+        <v>-9.375</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J19" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>16</v>
+        <v>17.543859649122</v>
       </c>
       <c r="L19" s="15">
-        <v>38.095238095238</v>
+        <v>36.734693877551</v>
       </c>
       <c r="M19" s="15">
-        <v>132</v>
+        <v>148.148148148148</v>
       </c>
       <c r="N19" s="15">
-        <v>31.818181818181</v>
+        <v>26.415094339622</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
+        <v>-88.888888888888</v>
+      </c>
+      <c r="M20" s="15">
         <v>-87.5</v>
       </c>
-      <c r="M20" s="15">
-        <v>-85.714285714285</v>
-      </c>
       <c r="N20" s="15">
-        <v>-98</v>
+        <v>-98.113207547169</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-15.384615384615</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.432835820895</v>
+        <v>-18.421052631578</v>
       </c>
       <c r="I21" s="17">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="J21" s="17">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="K21" s="18">
-        <v>5.940594059405</v>
+        <v>1.626016260162</v>
       </c>
       <c r="L21" s="18">
-        <v>-1.834862385321</v>
+        <v>3.305785123966</v>
       </c>
       <c r="M21" s="18">
-        <v>57.352941176470</v>
+        <v>62.337662337662</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.874015748031</v>
+        <v>-57.482993197278</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="L22" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>5</v>
+      </c>
+      <c r="D23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>55.555555555555</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K23" s="15">
-        <v>52.941176470588</v>
+        <v>47.619047619047</v>
       </c>
       <c r="L23" s="15">
-        <v>44.444444444444</v>
+        <v>55</v>
       </c>
       <c r="M23" s="15">
-        <v>73.333333333333</v>
+        <v>55</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E24" s="15">
-        <v>-15</v>
+        <v>-31.034482758620</v>
       </c>
       <c r="F24" s="14">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
         <v>87</v>
       </c>
       <c r="H24" s="15">
-        <v>5.747126436781</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I24" s="14">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="J24" s="14">
-        <v>123</v>
+        <v>152</v>
       </c>
       <c r="K24" s="15">
-        <v>17.886178861788</v>
+        <v>7.236842105263</v>
       </c>
       <c r="L24" s="15">
-        <v>5.839416058394</v>
+        <v>5.844155844155</v>
       </c>
       <c r="M24" s="15">
-        <v>79.012345679012</v>
+        <v>83.146067415730</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.714285714285</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G25" s="14">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>-3.846153846153</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="K25" s="15">
-        <v>12.121212121212</v>
+        <v>2.352941176470</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.777777777777</v>
+        <v>-12.121212121212</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>-22.222222222222</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J26" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K26" s="15">
-        <v>-16.981132075471</v>
+        <v>-18.032786885245</v>
       </c>
       <c r="L26" s="15">
-        <v>-20</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M26" s="15">
-        <v>22.222222222222</v>
+        <v>28.205128205128</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I28" s="14">
         <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>-100</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>-100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
+      </c>
+      <c r="L31" s="15">
+        <v>0</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -904,11 +904,11 @@
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>-100</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-22.222222222222</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>-23.076923076923</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L16" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M16" s="15">
-        <v>-44.444444444444</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.452991452991</v>
+        <v>-91.472868217054</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>-44.444444444444</v>
+        <v>-40</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="K17" s="15">
-        <v>-7.407407407407</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.242424242424</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M17" s="15">
-        <v>78.571428571428</v>
+        <v>87.5</v>
       </c>
       <c r="N17" s="15">
-        <v>31.578947368421</v>
+        <v>36.363636363636</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
         <v>0</v>
       </c>
       <c r="F18" s="14">
+        <v>14</v>
+      </c>
+      <c r="G18" s="14">
+        <v>13</v>
+      </c>
+      <c r="H18" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="I18" s="14">
+        <v>23</v>
+      </c>
+      <c r="J18" s="14">
+        <v>24</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-4.166666666666</v>
+      </c>
+      <c r="L18" s="15">
         <v>15</v>
       </c>
-      <c r="G18" s="14">
-        <v>14</v>
-      </c>
-      <c r="H18" s="15">
-        <v>7.142857142857</v>
-      </c>
-      <c r="I18" s="14">
-        <v>21</v>
-      </c>
-      <c r="J18" s="14">
-        <v>22</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-4.545454545454</v>
-      </c>
-      <c r="L18" s="15">
-        <v>31.25</v>
-      </c>
       <c r="M18" s="15">
-        <v>200</v>
+        <v>187.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-57.142857142857</v>
+        <v>-60.344827586206</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>28.571428571428</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
         <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.375</v>
+        <v>16</v>
       </c>
       <c r="I19" s="14">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K19" s="15">
-        <v>17.543859649122</v>
+        <v>22.950819672131</v>
       </c>
       <c r="L19" s="15">
-        <v>36.734693877551</v>
+        <v>36.363636363636</v>
       </c>
       <c r="M19" s="15">
-        <v>148.148148148148</v>
+        <v>127.272727272727</v>
       </c>
       <c r="N19" s="15">
-        <v>26.415094339622</v>
+        <v>31.578947368421</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1109,11 +1109,11 @@
       <c r="F20" s="14">
         <v>1</v>
       </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>0</v>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="14">
         <v>1</v>
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-88.888888888888</v>
+        <v>-90</v>
       </c>
       <c r="M20" s="15">
         <v>-87.5</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.113207547169</v>
+        <v>-98.461538461538</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17">
         <v>17</v>
       </c>
-      <c r="D21" s="17">
-        <v>22</v>
-      </c>
       <c r="E21" s="18">
-        <v>-22.727272727272</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F21" s="17">
         <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.421052631578</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="J21" s="17">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>1.626016260162</v>
+        <v>0.714285714285</v>
       </c>
       <c r="L21" s="18">
-        <v>3.305785123966</v>
+        <v>1.438848920863</v>
       </c>
       <c r="M21" s="18">
-        <v>62.337662337662</v>
+        <v>62.068965517241</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.482993197278</v>
+        <v>-57.910447761194</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1198,19 +1198,19 @@
         <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
         <v>5</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
       <c r="E23" s="15">
-        <v>25</v>
+        <v>-20</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H23" s="15">
-        <v>55.555555555555</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J23" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>47.619047619047</v>
+        <v>34.615384615384</v>
       </c>
       <c r="L23" s="15">
-        <v>55</v>
+        <v>20.689655172413</v>
       </c>
       <c r="M23" s="15">
-        <v>55</v>
+        <v>52.173913043478</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-31.034482758620</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="G24" s="14">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>3.448275862068</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="I24" s="14">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="J24" s="14">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="K24" s="15">
-        <v>7.236842105263</v>
+        <v>3.508771929824</v>
       </c>
       <c r="L24" s="15">
-        <v>5.844155844155</v>
+        <v>0.568181818181</v>
       </c>
       <c r="M24" s="15">
-        <v>83.146067415730</v>
+        <v>78.787878787878</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-31.578947368421</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="J25" s="14">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="K25" s="15">
-        <v>2.352941176470</v>
+        <v>-2.020202020202</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.121212121212</v>
+        <v>-11.009174311926</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
         <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
         <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.684210526315</v>
+        <v>-17.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J26" s="14">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="K26" s="15">
-        <v>-18.032786885245</v>
+        <v>-14.492753623188</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.076923076923</v>
+        <v>-23.376623376623</v>
       </c>
       <c r="M26" s="15">
-        <v>28.205128205128</v>
+        <v>31.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-100</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1447,13 +1447,13 @@
         <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="L31" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -937,10 +937,10 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
@@ -952,22 +952,22 @@
         <v>-45.454545454545</v>
       </c>
       <c r="I16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.888888888888</v>
+        <v>-40</v>
       </c>
       <c r="L16" s="15">
-        <v>-15.384615384615</v>
+        <v>-20</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.105263157894</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.472868217054</v>
+        <v>-91.489361702127</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-16.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-40</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J17" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L17" s="15">
-        <v>-23.076923076923</v>
+        <v>-24.390243902439</v>
       </c>
       <c r="M17" s="15">
-        <v>87.5</v>
+        <v>34.782608695652</v>
       </c>
       <c r="N17" s="15">
-        <v>36.363636363636</v>
+        <v>14.814814814814</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
+        <v>11</v>
+      </c>
+      <c r="G18" s="14">
+        <v>11</v>
+      </c>
+      <c r="H18" s="15">
         <v>0</v>
       </c>
-      <c r="F18" s="14">
-        <v>14</v>
-      </c>
-      <c r="G18" s="14">
-        <v>13</v>
-      </c>
-      <c r="H18" s="15">
-        <v>7.692307692307</v>
-      </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K18" s="15">
-        <v>-4.166666666666</v>
+        <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>15</v>
+        <v>8.695652173913</v>
       </c>
       <c r="M18" s="15">
-        <v>187.5</v>
+        <v>150</v>
       </c>
       <c r="N18" s="15">
-        <v>-60.344827586206</v>
+        <v>-60.317460317460</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>16</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I19" s="14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="K19" s="15">
-        <v>22.950819672131</v>
+        <v>12.676056338028</v>
       </c>
       <c r="L19" s="15">
-        <v>36.363636363636</v>
+        <v>23.076923076923</v>
       </c>
       <c r="M19" s="15">
-        <v>127.272727272727</v>
+        <v>116.216216216216</v>
       </c>
       <c r="N19" s="15">
-        <v>31.578947368421</v>
+        <v>26.984126984127</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,8 +1106,8 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G20" s="13" t="s">
         <v>20</v>
@@ -1128,10 +1128,10 @@
         <v>-90</v>
       </c>
       <c r="M20" s="15">
-        <v>-87.5</v>
+        <v>-88.888888888888</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.461538461538</v>
+        <v>-98.571428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-5.882352941176</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.428571428571</v>
+        <v>-19.402985074626</v>
       </c>
       <c r="I21" s="17">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="K21" s="18">
-        <v>0.714285714285</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L21" s="18">
-        <v>1.438848920863</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M21" s="18">
-        <v>62.068965517241</v>
+        <v>44.230769230769</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.910447761194</v>
+        <v>-59.239130434782</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1201,13 +1201,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>133.333333333333</v>
+        <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M22" s="15">
         <v>250</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G23" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
+        <v>27.272727272727</v>
+      </c>
+      <c r="I23" s="14">
+        <v>36</v>
+      </c>
+      <c r="J23" s="14">
+        <v>27</v>
+      </c>
+      <c r="K23" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="I23" s="14">
-        <v>35</v>
-      </c>
-      <c r="J23" s="14">
-        <v>26</v>
-      </c>
-      <c r="K23" s="15">
-        <v>34.615384615384</v>
-      </c>
       <c r="L23" s="15">
-        <v>20.689655172413</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>52.173913043478</v>
+        <v>44</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-21.052631578947</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.433734939759</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="I24" s="14">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="J24" s="14">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>3.508771929824</v>
+        <v>5.405405405405</v>
       </c>
       <c r="L24" s="15">
-        <v>0.568181818181</v>
+        <v>1.5625</v>
       </c>
       <c r="M24" s="15">
-        <v>78.787878787878</v>
+        <v>80.555555555555</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>-28.571428571428</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G25" s="14">
         <v>54</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="I25" s="14">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="J25" s="14">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="K25" s="15">
-        <v>-2.020202020202</v>
+        <v>2.830188679245</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.009174311926</v>
+        <v>-9.917355371900</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>-17.142857142857</v>
+        <v>32</v>
       </c>
       <c r="I26" s="14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J26" s="14">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="K26" s="15">
-        <v>-14.492753623188</v>
+        <v>-6.944444444444</v>
       </c>
       <c r="L26" s="15">
-        <v>-23.376623376623</v>
+        <v>-22.093023255814</v>
       </c>
       <c r="M26" s="15">
-        <v>31.111111111111</v>
+        <v>39.583333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,19 +1438,19 @@
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>3</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-62.5</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="L28" s="15">
         <v>-25</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-80</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-45.454545454545</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K16" s="15">
-        <v>-40</v>
+        <v>-48</v>
       </c>
       <c r="L16" s="15">
-        <v>-20</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.454545454545</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.489361702127</v>
+        <v>-91.612903225806</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>40</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I17" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.428571428571</v>
+        <v>-5</v>
       </c>
       <c r="L17" s="15">
-        <v>-24.390243902439</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="M17" s="15">
-        <v>34.782608695652</v>
+        <v>35.714285714285</v>
       </c>
       <c r="N17" s="15">
-        <v>14.814814814814</v>
+        <v>35.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>11</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>8.695652173913</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M18" s="15">
-        <v>150</v>
+        <v>154.545454545455</v>
       </c>
       <c r="N18" s="15">
-        <v>-60.317460317460</v>
+        <v>-57.575757575757</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
+        <v>30</v>
+      </c>
+      <c r="G19" s="14">
         <v>25</v>
       </c>
-      <c r="G19" s="14">
-        <v>27</v>
-      </c>
       <c r="H19" s="15">
-        <v>-7.407407407407</v>
+        <v>20</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>12.676056338028</v>
+        <v>17.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>23.076923076923</v>
+        <v>25.714285714285</v>
       </c>
       <c r="M19" s="15">
-        <v>116.216216216216</v>
+        <v>109.52380952381</v>
       </c>
       <c r="N19" s="15">
-        <v>26.984126984127</v>
+        <v>25.714285714285</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
+      </c>
+      <c r="F20" s="14">
+        <v>1</v>
+      </c>
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15">
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-90</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-88.888888888888</v>
+        <v>-80</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.571428571428</v>
+        <v>-97.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.402985074626</v>
+        <v>-13.888888888888</v>
       </c>
       <c r="I21" s="17">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="J21" s="17">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.225806451612</v>
+        <v>-1.734104046242</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.846153846153</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="M21" s="18">
-        <v>44.230769230769</v>
+        <v>45.299145299145</v>
       </c>
       <c r="N21" s="18">
-        <v>-59.239130434782</v>
+        <v>-57.286432160804</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L22" s="15">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="M22" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F23" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>27.272727272727</v>
+        <v>20</v>
       </c>
       <c r="I23" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="J23" s="14">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>37.5</v>
       </c>
       <c r="L23" s="15">
-        <v>9.090909090909</v>
+        <v>10</v>
       </c>
       <c r="M23" s="15">
-        <v>44</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
         <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G24" s="14">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.853658536585</v>
+        <v>-3.947368421052</v>
       </c>
       <c r="I24" s="14">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="K24" s="15">
-        <v>5.405405405405</v>
+        <v>8.040201005025</v>
       </c>
       <c r="L24" s="15">
-        <v>1.5625</v>
+        <v>3.365384615384</v>
       </c>
       <c r="M24" s="15">
-        <v>80.555555555555</v>
+        <v>79.166666666666</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
         <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>71.428571428571</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F25" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="H25" s="15">
-        <v>-18.518518518518</v>
+        <v>-4.255319148936</v>
       </c>
       <c r="I25" s="14">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="J25" s="14">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K25" s="15">
-        <v>2.830188679245</v>
+        <v>5.309734513274</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.917355371900</v>
+        <v>-9.848484848484</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>166.666666666667</v>
+        <v>450</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>32</v>
+        <v>61.904761904761</v>
       </c>
       <c r="I26" s="14">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J26" s="14">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.944444444444</v>
+        <v>5.405405405405</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.093023255814</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>39.583333333333</v>
+        <v>39.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" s="14">
         <v>1</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-72.727272727272</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-80</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
         <v>14</v>
       </c>
       <c r="H16" s="15">
-        <v>-71.428571428571</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I16" s="14">
         <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-48</v>
+        <v>-51.851851851851</v>
       </c>
       <c r="L16" s="15">
-        <v>-13.333333333333</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="15">
-        <v>-43.478260869565</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.612903225806</v>
+        <v>-92.215568862275</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-27.272727272727</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-19.148936170212</v>
+        <v>-16.981132075471</v>
       </c>
       <c r="M17" s="15">
-        <v>35.714285714285</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N17" s="15">
-        <v>35.714285714285</v>
+        <v>41.935483870967</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>10</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
         <v>0</v>
       </c>
       <c r="L18" s="15">
-        <v>-3.448275862068</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="M18" s="15">
-        <v>154.545454545455</v>
+        <v>123.076923076923</v>
       </c>
       <c r="N18" s="15">
-        <v>-57.575757575757</v>
+        <v>-57.971014492753</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>20</v>
+        <v>18.518518518518</v>
       </c>
       <c r="I19" s="14">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="K19" s="15">
-        <v>17.333333333333</v>
+        <v>17.857142857142</v>
       </c>
       <c r="L19" s="15">
-        <v>25.714285714285</v>
+        <v>25.316455696202</v>
       </c>
       <c r="M19" s="15">
-        <v>109.52380952381</v>
+        <v>120</v>
       </c>
       <c r="N19" s="15">
-        <v>25.714285714285</v>
+        <v>11.235955056179</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>1</v>
@@ -1131,7 +1131,7 @@
         <v>-80</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.333333333333</v>
+        <v>-97.435897435897</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>6.25</v>
       </c>
       <c r="F21" s="17">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G21" s="17">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.888888888888</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I21" s="17">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="J21" s="17">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.734104046242</v>
+        <v>-0.529100529100</v>
       </c>
       <c r="L21" s="18">
-        <v>-2.857142857142</v>
+        <v>-6.467661691542</v>
       </c>
       <c r="M21" s="18">
-        <v>45.299145299145</v>
+        <v>49.206349206349</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.286432160804</v>
+        <v>-57.175398633257</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
         <v>3</v>
       </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
       <c r="H22" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>166.666666666667</v>
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
         <v>18</v>
@@ -1239,19 +1239,19 @@
         <v>20</v>
       </c>
       <c r="I23" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
-        <v>37.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>10</v>
+        <v>11.627906976744</v>
       </c>
       <c r="M23" s="15">
-        <v>51.724137931034</v>
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E24" s="15">
-        <v>42.857142857142</v>
+        <v>4.761904761904</v>
       </c>
       <c r="F24" s="14">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-3.947368421052</v>
+        <v>10.294117647058</v>
       </c>
       <c r="I24" s="14">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="J24" s="14">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="K24" s="15">
-        <v>8.040201005025</v>
+        <v>7.727272727272</v>
       </c>
       <c r="L24" s="15">
-        <v>3.365384615384</v>
+        <v>-0.420168067226</v>
       </c>
       <c r="M24" s="15">
-        <v>79.166666666666</v>
+        <v>82.307692307692</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E25" s="15">
-        <v>42.857142857142</v>
+        <v>15.384615384615</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G25" s="14">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-4.255319148936</v>
+        <v>14.634146341463</v>
       </c>
       <c r="I25" s="14">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="J25" s="14">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="K25" s="15">
-        <v>5.309734513274</v>
+        <v>6.349206349206</v>
       </c>
       <c r="L25" s="15">
-        <v>-9.848484848484</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>61.904761904761</v>
+        <v>123.529411764706</v>
       </c>
       <c r="I26" s="14">
+        <v>88</v>
+      </c>
+      <c r="J26" s="14">
         <v>78</v>
       </c>
-      <c r="J26" s="14">
-        <v>74</v>
-      </c>
       <c r="K26" s="15">
-        <v>5.405405405405</v>
+        <v>12.820512820512</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.285714285714</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>39.285714285714</v>
+        <v>46.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
+        <v>4</v>
+      </c>
+      <c r="H28" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I28" s="14">
         <v>6</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-83.333333333333</v>
-      </c>
-      <c r="I28" s="14">
-        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-63.636363636363</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L28" s="15">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,13 +1570,13 @@
         <v>1</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L31" s="15">
-        <v>-66.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>-78.571428571428</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K16" s="15">
-        <v>-51.851851851851</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.578947368421</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-50</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.215568862275</v>
+        <v>-91.935483870967</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>11.764705882352</v>
+        <v>12.5</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.981132075471</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M17" s="15">
-        <v>51.724137931034</v>
+        <v>60</v>
       </c>
       <c r="N17" s="15">
-        <v>41.935483870967</v>
+        <v>26.315789473684</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>0</v>
+        <v>6.451612903225</v>
       </c>
       <c r="L18" s="15">
-        <v>-19.444444444444</v>
+        <v>-10.810810810810</v>
       </c>
       <c r="M18" s="15">
-        <v>123.076923076923</v>
+        <v>135.714285714286</v>
       </c>
       <c r="N18" s="15">
-        <v>-57.971014492753</v>
+        <v>-58.227848101265</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>22.222222222222</v>
+        <v>175</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
         <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>18.518518518518</v>
+        <v>29.629629629629</v>
       </c>
       <c r="I19" s="14">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K19" s="15">
-        <v>17.857142857142</v>
+        <v>25</v>
       </c>
       <c r="L19" s="15">
-        <v>25.316455696202</v>
+        <v>26.436781609195</v>
       </c>
       <c r="M19" s="15">
-        <v>120</v>
+        <v>115.686274509804</v>
       </c>
       <c r="N19" s="15">
-        <v>11.235955056179</v>
+        <v>8.910891089108</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1128,10 +1128,10 @@
         <v>-83.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-80</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.435897435897</v>
+        <v>-97.701149425287</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>6.25</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F21" s="17">
+        <v>68</v>
+      </c>
+      <c r="G21" s="17">
         <v>63</v>
       </c>
-      <c r="G21" s="17">
-        <v>66</v>
-      </c>
       <c r="H21" s="18">
-        <v>-4.545454545454</v>
+        <v>7.936507936507</v>
       </c>
       <c r="I21" s="17">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.529100529100</v>
+        <v>2.955665024630</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.467661691542</v>
+        <v>-3.240740740740</v>
       </c>
       <c r="M21" s="18">
-        <v>49.206349206349</v>
+        <v>52.554744525547</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.175398633257</v>
+        <v>-57.862903225806</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1221,10 +1221,10 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
         <v>0</v>
@@ -1233,25 +1233,25 @@
         <v>18</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>20</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I23" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J23" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K23" s="15">
         <v>33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>11.627906976744</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>57.575757575757</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D24" s="14">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="E24" s="15">
-        <v>4.761904761904</v>
+        <v>-30</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H24" s="15">
-        <v>10.294117647058</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="J24" s="14">
-        <v>220</v>
+        <v>250</v>
       </c>
       <c r="K24" s="15">
-        <v>7.727272727272</v>
+        <v>2.8</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.420168067226</v>
+        <v>-2.281368821292</v>
       </c>
       <c r="M24" s="15">
-        <v>82.307692307692</v>
+        <v>76.027397260274</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>15.384615384615</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F25" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>14.634146341463</v>
+        <v>-10.204081632653</v>
       </c>
       <c r="I25" s="14">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="J25" s="14">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="K25" s="15">
-        <v>6.349206349206</v>
+        <v>-4.054054054054</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.987012987013</v>
+        <v>-16.959064327485</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>-37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
         <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>123.529411764706</v>
+        <v>94.117647058823</v>
       </c>
       <c r="I26" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K26" s="15">
-        <v>12.820512820512</v>
+        <v>6.976744186046</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.333333333333</v>
+        <v>-13.207547169811</v>
       </c>
       <c r="M26" s="15">
-        <v>46.666666666666</v>
+        <v>37.313432835820</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-45.454545454545</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,8 +1493,8 @@
       <c r="K29" s="15">
         <v>-100</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-100</v>
       </c>
       <c r="M29" s="15">
         <v>-100</v>
@@ -1534,8 +1534,8 @@
       <c r="K30" s="15">
         <v>-100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>-100</v>
       </c>
       <c r="M30" s="15">
         <v>-100</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="14">
-        <v>2</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>3</v>
       </c>
       <c r="K31" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-80</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>-75</v>
       </c>
       <c r="M15" s="15">
         <v>-50</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
+        <v>6</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F16" s="14">
-        <v>4</v>
-      </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H16" s="15">
-        <v>-66.666666666666</v>
+        <v>-81.25</v>
       </c>
       <c r="I16" s="14">
         <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>-50</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-46.428571428571</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.935483870967</v>
+        <v>-92.537313432835</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>12.5</v>
+        <v>-12.5</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.040816326530</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.789473684210</v>
+        <v>-11.864406779661</v>
       </c>
       <c r="M17" s="15">
-        <v>60</v>
+        <v>48.571428571428</v>
       </c>
       <c r="N17" s="15">
-        <v>26.315789473684</v>
+        <v>13.043478260869</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="F18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>42.857142857142</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I18" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>6.451612903225</v>
+        <v>21.875</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.810810810810</v>
+        <v>2.631578947368</v>
       </c>
       <c r="M18" s="15">
-        <v>135.714285714286</v>
+        <v>160</v>
       </c>
       <c r="N18" s="15">
-        <v>-58.227848101265</v>
+        <v>-53.571428571428</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D19" s="14">
         <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>175</v>
+        <v>300</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>29.629629629629</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="J19" s="14">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K19" s="15">
-        <v>25</v>
+        <v>35.869565217391</v>
       </c>
       <c r="L19" s="15">
-        <v>26.436781609195</v>
+        <v>32.978723404255</v>
       </c>
       <c r="M19" s="15">
-        <v>115.686274509804</v>
+        <v>115.51724137931</v>
       </c>
       <c r="N19" s="15">
-        <v>8.910891089108</v>
+        <v>11.607142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>-81.818181818181</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.701149425287</v>
+        <v>-97.849462365591</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>35.714285714285</v>
+        <v>23.809523809523</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>7.936507936507</v>
+        <v>20.289855072463</v>
       </c>
       <c r="I21" s="17">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="K21" s="18">
-        <v>2.955665024630</v>
+        <v>4.464285714285</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.240740740740</v>
+        <v>0.429184549356</v>
       </c>
       <c r="M21" s="18">
-        <v>52.554744525547</v>
+        <v>52.941176470588</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.862903225806</v>
+        <v>-56.746765249537</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,10 +1192,10 @@
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1224,34 +1224,34 @@
         <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E23" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F23" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>38.461538461538</v>
+        <v>11.764705882352</v>
       </c>
       <c r="I23" s="14">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J23" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="L23" s="15">
-        <v>8.333333333333</v>
+        <v>5.769230769230</v>
       </c>
       <c r="M23" s="15">
-        <v>57.575757575757</v>
+        <v>48.648648648648</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-30</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="F24" s="14">
         <v>79</v>
       </c>
       <c r="G24" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-4.819277108433</v>
       </c>
       <c r="I24" s="14">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="J24" s="14">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="K24" s="15">
-        <v>2.8</v>
+        <v>2.238805970149</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.281368821292</v>
+        <v>-4.529616724738</v>
       </c>
       <c r="M24" s="15">
-        <v>76.027397260274</v>
+        <v>73.417721518987</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>13</v>
+      </c>
+      <c r="D25" s="14">
         <v>8</v>
       </c>
-      <c r="D25" s="14">
-        <v>22</v>
-      </c>
       <c r="E25" s="15">
-        <v>-63.636363636363</v>
+        <v>62.5</v>
       </c>
       <c r="F25" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H25" s="15">
-        <v>-10.204081632653</v>
+        <v>-10</v>
       </c>
       <c r="I25" s="14">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="J25" s="14">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="K25" s="15">
-        <v>-4.054054054054</v>
+        <v>-0.641025641025</v>
       </c>
       <c r="L25" s="15">
-        <v>-16.959064327485</v>
+        <v>-14.364640883977</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E26" s="15">
-        <v>-37.5</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>94.117647058823</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I26" s="14">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="J26" s="14">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>6.976744186046</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.207547169811</v>
+        <v>-8.849557522123</v>
       </c>
       <c r="M26" s="15">
-        <v>37.313432835820</v>
+        <v>35.526315789473</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>-60</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,31 +1426,31 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
         <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-38.461538461538</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
         <v>-75</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
       <c r="G16" s="14">
+        <v>13</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-76.923076923076</v>
+      </c>
+      <c r="I16" s="14">
         <v>16</v>
       </c>
-      <c r="H16" s="15">
-        <v>-81.25</v>
-      </c>
-      <c r="I16" s="14">
-        <v>15</v>
-      </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>-58.333333333333</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-40.740740740740</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.275862068965</v>
+        <v>-51.515151515151</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.537313432835</v>
+        <v>-92.626728110599</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
+        <v>-28</v>
+      </c>
+      <c r="I17" s="14">
+        <v>56</v>
+      </c>
+      <c r="J17" s="14">
+        <v>65</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-13.846153846153</v>
+      </c>
+      <c r="L17" s="15">
         <v>-12.5</v>
       </c>
-      <c r="I17" s="14">
-        <v>52</v>
-      </c>
-      <c r="J17" s="14">
-        <v>59</v>
-      </c>
-      <c r="K17" s="15">
-        <v>-11.864406779661</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-11.864406779661</v>
-      </c>
       <c r="M17" s="15">
-        <v>48.571428571428</v>
+        <v>43.589743589743</v>
       </c>
       <c r="N17" s="15">
-        <v>13.043478260869</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>6</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>500</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>85.714285714285</v>
+        <v>80</v>
       </c>
       <c r="I18" s="14">
         <v>39</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>21.875</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>2.631578947368</v>
+        <v>-2.5</v>
       </c>
       <c r="M18" s="15">
-        <v>160</v>
+        <v>143.75</v>
       </c>
       <c r="N18" s="15">
-        <v>-53.571428571428</v>
+        <v>-56.666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>300</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
         <v>45</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>114.285714285714</v>
+        <v>87.5</v>
       </c>
       <c r="I19" s="14">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J19" s="14">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>35.869565217391</v>
+        <v>34.343434343434</v>
       </c>
       <c r="L19" s="15">
-        <v>32.978723404255</v>
+        <v>25.471698113207</v>
       </c>
       <c r="M19" s="15">
-        <v>115.51724137931</v>
+        <v>125.423728813559</v>
       </c>
       <c r="N19" s="15">
-        <v>11.607142857142</v>
+        <v>9.917355371900</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1106,14 +1106,14 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="14">
-        <v>1</v>
-      </c>
-      <c r="G20" s="14">
-        <v>1</v>
-      </c>
-      <c r="H20" s="15">
-        <v>0</v>
+      <c r="F20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I20" s="14">
         <v>2</v>
@@ -1128,10 +1128,10 @@
         <v>-85.714285714285</v>
       </c>
       <c r="M20" s="15">
-        <v>-84.615384615384</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N20" s="15">
-        <v>-97.849462365591</v>
+        <v>-98.039215686274</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>23.809523809523</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="F21" s="17">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>20.289855072463</v>
+        <v>10.294117647058</v>
       </c>
       <c r="I21" s="17">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="J21" s="17">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="K21" s="18">
-        <v>4.464285714285</v>
+        <v>2.489626556016</v>
       </c>
       <c r="L21" s="18">
-        <v>0.429184549356</v>
+        <v>-3.137254901960</v>
       </c>
       <c r="M21" s="18">
-        <v>52.941176470588</v>
+        <v>50.609756097561</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.746765249537</v>
+        <v>-57.777777777777</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
+        <v>-75</v>
+      </c>
+      <c r="I22" s="14">
+        <v>9</v>
+      </c>
+      <c r="J22" s="14">
+        <v>9</v>
+      </c>
+      <c r="K22" s="15">
         <v>0</v>
       </c>
-      <c r="I22" s="14">
-        <v>8</v>
-      </c>
-      <c r="J22" s="14">
-        <v>6</v>
-      </c>
-      <c r="K22" s="15">
-        <v>33.333333333333</v>
-      </c>
       <c r="L22" s="15">
-        <v>166.666666666667</v>
+        <v>125</v>
       </c>
       <c r="M22" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-40</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>11.764705882352</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J23" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K23" s="15">
-        <v>25</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L23" s="15">
-        <v>5.769230769230</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="M23" s="15">
-        <v>48.648648648648</v>
+        <v>40</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-5.555555555555</v>
+        <v>21.052631578947</v>
       </c>
       <c r="F24" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G24" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H24" s="15">
-        <v>-4.819277108433</v>
+        <v>-5.681818181818</v>
       </c>
       <c r="I24" s="14">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="J24" s="14">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="K24" s="15">
-        <v>2.238805970149</v>
+        <v>3.484320557491</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.529616724738</v>
+        <v>-6.603773584905</v>
       </c>
       <c r="M24" s="15">
-        <v>73.417721518987</v>
+        <v>70.689655172413</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>62.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G25" s="14">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H25" s="15">
-        <v>-10</v>
+        <v>-2.040816326530</v>
       </c>
       <c r="I25" s="14">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J25" s="14">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="K25" s="15">
-        <v>-0.641025641025</v>
+        <v>3.086419753086</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.364640883977</v>
+        <v>-15.228426395939</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-35.294117647058</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H26" s="15">
-        <v>16.129032258064</v>
+        <v>-13.157894736842</v>
       </c>
       <c r="I26" s="14">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>-0.892857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.849557522123</v>
+        <v>-11.2</v>
       </c>
       <c r="M26" s="15">
-        <v>35.526315789473</v>
+        <v>33.734939759036</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>2</v>
       </c>
       <c r="J27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-35.714285714285</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1576,7 +1576,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L31" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -933,14 +933,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -955,19 +955,19 @@
         <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K16" s="15">
-        <v>-57.894736842105</v>
+        <v>-60</v>
       </c>
       <c r="L16" s="15">
-        <v>-40.740740740740</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="M16" s="15">
-        <v>-51.515151515151</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.626728110599</v>
+        <v>-93.043478260869</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-28</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K17" s="15">
-        <v>-13.846153846153</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="L17" s="15">
-        <v>-12.5</v>
+        <v>-16.901408450704</v>
       </c>
       <c r="M17" s="15">
-        <v>43.589743589743</v>
+        <v>47.5</v>
       </c>
       <c r="N17" s="15">
-        <v>12</v>
+        <v>7.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>18.181818181818</v>
+        <v>20</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.5</v>
+        <v>2.439024390243</v>
       </c>
       <c r="M18" s="15">
-        <v>143.75</v>
+        <v>162.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-56.666666666666</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>14.285714285714</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>87.5</v>
+        <v>104.761904761905</v>
       </c>
       <c r="I19" s="14">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="K19" s="15">
-        <v>34.343434343434</v>
+        <v>35.238095238095</v>
       </c>
       <c r="L19" s="15">
-        <v>25.471698113207</v>
+        <v>23.478260869565</v>
       </c>
       <c r="M19" s="15">
-        <v>125.423728813559</v>
+        <v>129.032258064516</v>
       </c>
       <c r="N19" s="15">
-        <v>9.917355371900</v>
+        <v>10.9375</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>2</v>
+      </c>
+      <c r="G20" s="14">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15">
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-85.714285714285</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>-85.714285714285</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-98.039215686274</v>
+        <v>-96.363636363636</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,54 +1139,54 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="17">
-        <v>17</v>
-      </c>
       <c r="E21" s="18">
-        <v>-29.411764705882</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>10.294117647058</v>
+        <v>14.0625</v>
       </c>
       <c r="I21" s="17">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="J21" s="17">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>2.489626556016</v>
+        <v>4.347826086956</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.137254901960</v>
+        <v>-4</v>
       </c>
       <c r="M21" s="18">
-        <v>50.609756097561</v>
+        <v>50.857142857142</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.777777777777</v>
+        <v>-57.961783439490</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
@@ -1201,10 +1201,10 @@
         <v>9</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L22" s="15">
         <v>125</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>200</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I23" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J23" s="14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23" s="15">
-        <v>16.666666666666</v>
+        <v>20.408163265306</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.448275862068</v>
+        <v>-6.349206349206</v>
       </c>
       <c r="M23" s="15">
-        <v>40</v>
+        <v>47.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>21.052631578947</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="G24" s="14">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.681818181818</v>
+        <v>7.058823529411</v>
       </c>
       <c r="I24" s="14">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="J24" s="14">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="K24" s="15">
-        <v>3.484320557491</v>
+        <v>7.213114754098</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.603773584905</v>
+        <v>-6.303724928366</v>
       </c>
       <c r="M24" s="15">
-        <v>70.689655172413</v>
+        <v>75.806451612903</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>83.333333333333</v>
+        <v>70</v>
       </c>
       <c r="F25" s="14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" s="14">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-2.040816326530</v>
+        <v>8.695652173913</v>
       </c>
       <c r="I25" s="14">
-        <v>167</v>
+        <v>184</v>
       </c>
       <c r="J25" s="14">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="K25" s="15">
-        <v>3.086419753086</v>
+        <v>6.976744186046</v>
       </c>
       <c r="L25" s="15">
-        <v>-15.228426395939</v>
+        <v>-17.117117117117</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
         <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.157894736842</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="I26" s="14">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="K26" s="15">
-        <v>-0.892857142857</v>
+        <v>2.479338842975</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.2</v>
+        <v>-7.462686567164</v>
       </c>
       <c r="M26" s="15">
-        <v>33.734939759036</v>
+        <v>36.263736263736</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-26.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
-      <c r="H31" s="15">
-        <v>-50</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>2</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="13" t="s">
-        <v>20</v>
+      <c r="F33" s="14">
+        <v>1</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1625,8 +1625,8 @@
       <c r="H33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I33" s="13" t="s">
-        <v>20</v>
+      <c r="I33" s="14">
+        <v>1</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>
@@ -1635,7 +1635,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M33" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L15" s="15">
         <v>-75</v>
@@ -926,48 +926,48 @@
         <v>-50</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
+        <v>3</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F16" s="14">
         <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="14">
-        <v>3</v>
       </c>
       <c r="G16" s="14">
         <v>13</v>
       </c>
       <c r="H16" s="15">
-        <v>-76.923076923076</v>
+        <v>-84.615384615384</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>-60</v>
+        <v>-60.465116279069</v>
       </c>
       <c r="L16" s="15">
-        <v>-44.827586206896</v>
+        <v>-51.428571428571</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.974358974359</v>
+        <v>-58.536585365853</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.043478260869</v>
+        <v>-92.975206611570</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,63 +975,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
         <v>22</v>
       </c>
       <c r="H17" s="15">
-        <v>-40.909090909090</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="K17" s="15">
-        <v>-10.606060606060</v>
+        <v>-4.225352112676</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.901408450704</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="M17" s="15">
-        <v>47.5</v>
+        <v>54.545454545454</v>
       </c>
       <c r="N17" s="15">
-        <v>7.272727272727</v>
+        <v>15.254237288135</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>50</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I18" s="14">
         <v>42</v>
@@ -1043,13 +1043,13 @@
         <v>20</v>
       </c>
       <c r="L18" s="15">
-        <v>2.439024390243</v>
+        <v>-2.325581395348</v>
       </c>
       <c r="M18" s="15">
-        <v>162.5</v>
+        <v>147.058823529412</v>
       </c>
       <c r="N18" s="15">
-        <v>-58</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>104.761904761905</v>
+        <v>62.5</v>
       </c>
       <c r="I19" s="14">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="J19" s="14">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K19" s="15">
-        <v>35.238095238095</v>
+        <v>33.035714285714</v>
       </c>
       <c r="L19" s="15">
-        <v>23.478260869565</v>
+        <v>20.161290322580</v>
       </c>
       <c r="M19" s="15">
-        <v>129.032258064516</v>
+        <v>119.117647058824</v>
       </c>
       <c r="N19" s="15">
-        <v>10.9375</v>
+        <v>12.030075187969</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-73.333333333333</v>
+        <v>-78.947368421052</v>
       </c>
       <c r="M20" s="15">
-        <v>-73.333333333333</v>
+        <v>-80.952380952380</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.363636363636</v>
+        <v>-96.721311475409</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>14.0625</v>
+        <v>5.970149253731</v>
       </c>
       <c r="I21" s="17">
-        <v>264</v>
+        <v>281</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="K21" s="18">
-        <v>4.347826086956</v>
+        <v>4.074074074074</v>
       </c>
       <c r="L21" s="18">
-        <v>-4</v>
+        <v>-8.169934640522</v>
       </c>
       <c r="M21" s="18">
-        <v>50.857142857142</v>
+        <v>44.845360824742</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.961783439490</v>
+        <v>-57.871064467766</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>200</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-23.076923076923</v>
+        <v>7.142857142857</v>
       </c>
       <c r="I23" s="14">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J23" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K23" s="15">
-        <v>20.408163265306</v>
+        <v>26.415094339622</v>
       </c>
       <c r="L23" s="15">
-        <v>-6.349206349206</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="M23" s="15">
-        <v>47.5</v>
+        <v>48.888888888888</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E24" s="15">
-        <v>66.666666666666</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G24" s="14">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H24" s="15">
-        <v>7.058823529411</v>
+        <v>25.333333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="J24" s="14">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="K24" s="15">
-        <v>7.213114754098</v>
+        <v>8</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.303724928366</v>
+        <v>-7.387862796833</v>
       </c>
       <c r="M24" s="15">
-        <v>75.806451612903</v>
+        <v>72.906403940886</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E25" s="15">
-        <v>70</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H25" s="15">
-        <v>8.695652173913</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I25" s="14">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="J25" s="14">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="K25" s="15">
-        <v>6.976744186046</v>
+        <v>4.736842105263</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.117117117117</v>
+        <v>-17.768595041322</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G26" s="14">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H26" s="15">
-        <v>-11.627906976744</v>
+        <v>12.195121951219</v>
       </c>
       <c r="I26" s="14">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="J26" s="14">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K26" s="15">
-        <v>2.479338842975</v>
+        <v>7.874015748031</v>
       </c>
       <c r="L26" s="15">
-        <v>-7.462686567164</v>
+        <v>-8.053691275167</v>
       </c>
       <c r="M26" s="15">
-        <v>36.263736263736</v>
+        <v>41.237113402061</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1406,10 +1406,10 @@
         <v>2</v>
       </c>
       <c r="J27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
         <v>-75</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>12</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L28" s="15">
-        <v>20</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -914,10 +914,10 @@
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L15" s="15">
         <v>-75</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="14">
         <v>3</v>
       </c>
-      <c r="E16" s="15">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="F16" s="14">
-        <v>2</v>
-      </c>
       <c r="G16" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-84.615384615384</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
         <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>-60.465116279069</v>
+        <v>-55.813953488372</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.428571428571</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.536585365853</v>
+        <v>-53.658536585365</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.975206611570</v>
+        <v>-92.607003891050</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-13.636363636363</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.225352112676</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.049382716049</v>
+        <v>-9.411764705882</v>
       </c>
       <c r="M17" s="15">
-        <v>54.545454545454</v>
+        <v>57.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>15.254237288135</v>
+        <v>20.3125</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.325581395348</v>
+        <v>-2.173913043478</v>
       </c>
       <c r="M18" s="15">
-        <v>147.058823529412</v>
+        <v>164.705882352941</v>
       </c>
       <c r="N18" s="15">
-        <v>-60</v>
+        <v>-60.869565217391</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>18.181818181818</v>
       </c>
       <c r="F19" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>62.5</v>
+        <v>16.129032258064</v>
       </c>
       <c r="I19" s="14">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="J19" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K19" s="15">
-        <v>33.035714285714</v>
+        <v>31.707317073170</v>
       </c>
       <c r="L19" s="15">
-        <v>20.161290322580</v>
+        <v>26.5625</v>
       </c>
       <c r="M19" s="15">
-        <v>119.117647058824</v>
+        <v>128.169014084507</v>
       </c>
       <c r="N19" s="15">
-        <v>12.030075187969</v>
+        <v>17.391304347826</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,11 +1100,11 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
@@ -1131,7 +1131,7 @@
         <v>-80.952380952380</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.721311475409</v>
+        <v>-96.825396825396</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,72 +1139,72 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>31.578947368421</v>
       </c>
       <c r="F21" s="17">
         <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>5.970149253731</v>
+        <v>9.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="J21" s="17">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="K21" s="18">
-        <v>4.074074074074</v>
+        <v>6.574394463667</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.169934640522</v>
+        <v>-4.049844236760</v>
       </c>
       <c r="M21" s="18">
-        <v>44.845360824742</v>
+        <v>52.475247524752</v>
       </c>
       <c r="N21" s="18">
-        <v>-57.871064467766</v>
+        <v>-56.373937677053</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L22" s="15">
         <v>100</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>9</v>
+      </c>
+      <c r="D23" s="14">
         <v>8</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>12.5</v>
       </c>
       <c r="F23" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>7.142857142857</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I23" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J23" s="14">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="K23" s="15">
-        <v>26.415094339622</v>
+        <v>24.590163934426</v>
       </c>
       <c r="L23" s="15">
-        <v>-1.470588235294</v>
+        <v>4.109589041095</v>
       </c>
       <c r="M23" s="15">
-        <v>48.888888888888</v>
+        <v>58.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>18.518518518518</v>
       </c>
       <c r="F24" s="14">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H24" s="15">
-        <v>25.333333333333</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I24" s="14">
-        <v>351</v>
+        <v>381</v>
       </c>
       <c r="J24" s="14">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="K24" s="15">
-        <v>8</v>
+        <v>8.238636363636</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.387862796833</v>
+        <v>-5.459057071960</v>
       </c>
       <c r="M24" s="15">
-        <v>72.906403940886</v>
+        <v>75.576036866359</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="F25" s="14">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G25" s="14">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="H25" s="15">
-        <v>35.714285714285</v>
+        <v>13.725490196078</v>
       </c>
       <c r="I25" s="14">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="J25" s="14">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="K25" s="15">
-        <v>4.736842105263</v>
+        <v>3.381642512077</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.768595041322</v>
+        <v>-17.374517374517</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>116.666666666667</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G26" s="14">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>12.195121951219</v>
+        <v>62.068965517241</v>
       </c>
       <c r="I26" s="14">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="J26" s="14">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K26" s="15">
-        <v>7.874015748031</v>
+        <v>12.878787878787</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.053691275167</v>
+        <v>-3.246753246753</v>
       </c>
       <c r="M26" s="15">
-        <v>41.237113402061</v>
+        <v>46.078431372549</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1406,13 +1406,13 @@
         <v>2</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-29.411764705882</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L28" s="15">
-        <v>9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
+        <v>100</v>
+      </c>
+      <c r="L30" s="15">
+        <v>100</v>
+      </c>
+      <c r="M30" s="15">
         <v>0</v>
       </c>
-      <c r="L30" s="15">
-        <v>0</v>
-      </c>
-      <c r="M30" s="15">
-        <v>-50</v>
-      </c>
       <c r="N30" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-007pct.xlsx
+++ b/data/source/weekly/cs-en-us-007pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>4</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-57.142857142857</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K16" s="15">
-        <v>-55.813953488372</v>
+        <v>-57.446808510638</v>
       </c>
       <c r="L16" s="15">
-        <v>-51.282051282051</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.658536585365</v>
+        <v>-57.446808510638</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.607003891050</v>
+        <v>-92.647058823529</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>78.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J17" s="14">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>2.531645569620</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.411764705882</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="15">
-        <v>57.142857142857</v>
+        <v>55.769230769230</v>
       </c>
       <c r="N17" s="15">
-        <v>20.3125</v>
+        <v>9.459459459459</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>22.5</v>
       </c>
       <c r="L18" s="15">
-        <v>-2.173913043478</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
-        <v>164.705882352941</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-60.869565217391</v>
+        <v>-60.162601626016</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>18.181818181818</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G19" s="14">
         <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>16.129032258064</v>
+        <v>6.451612903225</v>
       </c>
       <c r="I19" s="14">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J19" s="14">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="K19" s="15">
-        <v>31.707317073170</v>
+        <v>28.461538461538</v>
       </c>
       <c r="L19" s="15">
-        <v>26.5625</v>
+        <v>20.143884892086</v>
       </c>
       <c r="M19" s="15">
-        <v>128.169014084507</v>
+        <v>128.767123287671</v>
       </c>
       <c r="N19" s="15">
-        <v>17.391304347826</v>
+        <v>12.080536912751</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="14">
+        <v>2</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
         <v>2</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>4</v>
       </c>
       <c r="J20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L20" s="15">
         <v>-78.947368421052</v>
       </c>
       <c r="M20" s="15">
-        <v>-80.952380952380</v>
+        <v>-82.608695652173</v>
       </c>
       <c r="N20" s="15">
-        <v>-96.825396825396</v>
+        <v>-96.946564885496</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
         <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>31.578947368421</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>9.230769230769</v>
+        <v>8.955223880597</v>
       </c>
       <c r="I21" s="17">
+        <v>322</v>
+      </c>
+      <c r="J21" s="17">
         <v>308</v>
       </c>
-      <c r="J21" s="17">
-        <v>289</v>
-      </c>
       <c r="K21" s="18">
-        <v>6.574394463667</v>
+        <v>4.545454545454</v>
       </c>
       <c r="L21" s="18">
-        <v>-4.049844236760</v>
+        <v>-5.571847507331</v>
       </c>
       <c r="M21" s="18">
-        <v>52.475247524752</v>
+        <v>47.031963470319</v>
       </c>
       <c r="N21" s="18">
-        <v>-56.373937677053</v>
+        <v>-57.350993377483</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,25 +1189,25 @@
         <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K22" s="15">
-        <v>-9.090909090909</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>233.333333333333</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>12.5</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>23.529411764705</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I23" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J23" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K23" s="15">
-        <v>24.590163934426</v>
+        <v>29.032258064516</v>
       </c>
       <c r="L23" s="15">
-        <v>4.109589041095</v>
+        <v>3.896103896103</v>
       </c>
       <c r="M23" s="15">
-        <v>58.333333333333</v>
+        <v>45.454545454545</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>18.518518518518</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="F24" s="14">
         <v>108</v>
       </c>
       <c r="G24" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>28.571428571428</v>
+        <v>18.681318681318</v>
       </c>
       <c r="I24" s="14">
-        <v>381</v>
+        <v>404</v>
       </c>
       <c r="J24" s="14">
-        <v>352</v>
+        <v>378</v>
       </c>
       <c r="K24" s="15">
-        <v>8.238636363636</v>
+        <v>6.878306878306</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.459057071960</v>
+        <v>-4.038004750593</v>
       </c>
       <c r="M24" s="15">
-        <v>75.576036866359</v>
+        <v>71.914893617021</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E25" s="15">
-        <v>-11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
         <v>58</v>
       </c>
       <c r="G25" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H25" s="15">
-        <v>13.725490196078</v>
+        <v>3.571428571428</v>
       </c>
       <c r="I25" s="14">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="J25" s="14">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="K25" s="15">
-        <v>3.381642512077</v>
+        <v>3.211009174311</v>
       </c>
       <c r="L25" s="15">
-        <v>-17.374517374517</v>
+        <v>-16.356877323420</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26" s="14">
         <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>62.068965517241</v>
+        <v>108</v>
       </c>
       <c r="I26" s="14">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="J26" s="14">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K26" s="15">
-        <v>12.878787878787</v>
+        <v>19.708029197080</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.246753246753</v>
+        <v>1.863354037267</v>
       </c>
       <c r="M26" s="15">
-        <v>46.078431372549</v>
+        <v>53.271028037383</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1426,13 +1426,13 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,16 +1444,16 @@
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J28" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K28" s="15">
-        <v>-27.777777777777</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
